--- a/results/final_results.xlsx
+++ b/results/final_results.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposed Model" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Comparison" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SHAP Importance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion Matrix Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fairness Evaluation" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,23 +482,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>CTGAN_250</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.992</v>
+        <v>0.995</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9777089783281736</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9350877192982456</v>
+        <v>0.9444</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9555054302422724</v>
+        <v>0.9843</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9909712835708764</v>
+        <v>0.9963</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,23 +512,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>CTGAN_500</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.991</v>
+        <v>0.995</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9694736842105264</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9350877192982456</v>
+        <v>0.9444</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9506198765022296</v>
+        <v>0.9843</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9805002306020044</v>
+        <v>0.9963</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,23 +542,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>CTGAN_250</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.989</v>
+        <v>0.995</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9682352941176472</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9134502923976608</v>
+        <v>0.9444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.938901098901099</v>
+        <v>0.9843</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9842777896717996</v>
+        <v>0.9956</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -570,23 +572,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>CTGAN_250</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.989</v>
+        <v>0.995</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8807017543859651</v>
+        <v>0.9444</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9360852219675748</v>
+        <v>0.9843</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9969075809654466</v>
+        <v>0.9942</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,23 +602,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>CTGAN_250</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.987</v>
+        <v>0.995</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9162573099415204</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9461988304093566</v>
+        <v>0.9444</v>
       </c>
       <c r="F6" t="n">
-        <v>0.930298719772404</v>
+        <v>0.9843</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9750167315157136</v>
+        <v>0.9933</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -630,25 +632,385 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>CTGAN_500</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9921</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CTGAN_500</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CTGAN_500</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9777089783281736</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9350877192982456</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9555054302422724</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9909712835708764</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9694736842105264</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9350877192982456</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9506198765022296</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9805002306020044</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CTGAN_500</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9418</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9682352941176472</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9134502923976608</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.938901098901099</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9842777896717996</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8807017543859651</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9360852219675748</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9969075809654466</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CTGAN_250</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7826</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9321</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9162573099415204</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9461988304093566</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.930298719772404</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9750167315157136</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CTGAN_500</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8095</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Decision Tree</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C18" t="n">
         <v>0.985</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D18" t="n">
         <v>0.9222222222222222</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E18" t="n">
         <v>0.924561403508772</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F18" t="n">
         <v>0.9203907203907205</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G18" t="n">
         <v>0.9578759904435972</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CTGAN_250</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.7727000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9167</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
@@ -665,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,7 +1083,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SMOTE</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -731,16 +1093,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9444</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.9843</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9984737484737484</v>
+        <v>0.9988</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9879227053140098</v>
+        <v>0.9899</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -764,16 +1126,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9444</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.9843</v>
       </c>
       <c r="G3" t="n">
-        <v>0.997863247863248</v>
+        <v>0.9983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9844444444444446</v>
+        <v>0.9861</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -787,7 +1149,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>SMOTE</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -797,18 +1159,315 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.9843</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9954212454212454</v>
+        <v>0.9979</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9747474747474748</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>Augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SMOTE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9974</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9815</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9954</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9747</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SMOTE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9951</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9739</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SMOTE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9908</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9653</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SMOTE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9701</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9530999999999999</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9494</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8095</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9471000000000001</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SMOTE</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8947000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9553</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Augmentation</t>
         </is>
@@ -873,7 +1532,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineered LightGBM</t>
+          <t>E-LightGBM (Proposed)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -886,13 +1545,13 @@
         <v>0.9444444444444444</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.9843444227005872</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9963369963369964</v>
+        <v>0.9966422466422468</v>
       </c>
       <c r="G2" t="n">
-        <v>0.977777777777778</v>
+        <v>0.978927203065134</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -964,23 +1623,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>CTGAN_250</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.992</v>
+        <v>0.995</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9777089783281736</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9350877192982456</v>
+        <v>0.9444</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9555054302422724</v>
+        <v>0.9843</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9909712835708764</v>
+        <v>0.9963</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -992,7 +1651,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SMOTE</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1002,16 +1661,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9444</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.9843</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9984737484737484</v>
+        <v>0.9988</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9879227053140098</v>
+        <v>0.9899</v>
       </c>
     </row>
     <row r="4">
@@ -1022,7 +1681,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Engineered LightGBM</t>
+          <t>E-LightGBM (Proposed)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1035,13 +1694,13 @@
         <v>0.9444444444444444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.9843444227005872</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9963369963369964</v>
+        <v>0.9966422466422468</v>
       </c>
       <c r="H4" t="n">
-        <v>0.977777777777778</v>
+        <v>0.978927203065134</v>
       </c>
     </row>
   </sheetData>
@@ -1055,7 +1714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,328 +1725,530 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mean |SHAP|</t>
+          <t>Mean_Abs_SHAP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Is_Composite</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>term_2_attendance</t>
+          <t>average_exam_score</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8262329127164341</v>
+        <v>0.5486638751290718</v>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>average_exam_score</t>
+          <t>term_2_attendance</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8262033329806061</v>
+        <v>0.438690771817454</v>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>family_income_level</t>
+          <t>attendance_risk_index</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5517736170220959</v>
+        <v>0.3205278108277316</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>term_1_attendance</t>
+          <t>family_income_level</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4112264836179576</v>
+        <v>0.2253171468470391</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>term_3_attendance</t>
+          <t>science_exam_score</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3567251070334827</v>
+        <v>0.1955371598332348</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>science_exam_score</t>
+          <t>term_1_attendance</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2816371505890119</v>
+        <v>0.1735002618625594</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>school_type</t>
+          <t>behavioral_engagement_index</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2269502414989457</v>
+        <v>0.1216896717155238</v>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>school_code</t>
+          <t>age_at_start_of_academic_year</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1444187278924625</v>
+        <v>0.1090445181666063</v>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>social_studies_exam_score</t>
+          <t>missed_school_due_to_illness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1114400425697534</v>
+        <v>0.0983760901249255</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>class_participation</t>
+          <t>school_code</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0994585086200459</v>
+        <v>0.090219501722153</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>safety_at_home</t>
+          <t>grade_repetition_count</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.091339274539236</v>
+        <v>0.08861070422147869</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>math_exam_score</t>
+          <t>class_participation</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0899222562444741</v>
+        <v>0.081695497273753</v>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>behaviour_warnings_punishments</t>
+          <t>travel_time_to_school</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0825987100755831</v>
+        <v>0.07656505179788289</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>age_at_start_of_academic_year</t>
+          <t>daily_study_hours_at_home</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0652547366752934</v>
+        <v>0.06769625099756681</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>no_of_siblings_in_school</t>
+          <t>term_3_attendance</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06401652241501191</v>
+        <v>0.0622722081634517</v>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>parent_guardian_education_level</t>
+          <t>safety_at_home</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0537499768509458</v>
+        <v>0.0618799478314891</v>
+      </c>
+      <c r="C17" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>grade_repetition_count</t>
+          <t>school_type</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0505844485227515</v>
+        <v>0.057633877592593</v>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>teacher_support_rating</t>
+          <t>social_studies_exam_score</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0339794117275052</v>
+        <v>0.05045490446948</v>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>english_exam_score</t>
+          <t>no_of_siblings_in_school</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0216867850166241</v>
+        <v>0.037562097406965</v>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>missed_school_due_to_illness</t>
+          <t>behaviour_warnings_punishments</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0215251685591925</v>
+        <v>0.0317610231997058</v>
+      </c>
+      <c r="C21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>parent_guardian_occupation</t>
+          <t>safety_at_school</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0173582718932859</v>
+        <v>0.0311595375312354</v>
+      </c>
+      <c r="C22" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>barriers_to_regular_attendance</t>
+          <t>parent_guardian_education_level</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0139760480014933</v>
+        <v>0.0286165568080508</v>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>own_textbooks</t>
+          <t>teacher_support_rating</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0103427190659471</v>
+        <v>0.0232104138079316</v>
+      </c>
+      <c r="C24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>parent_attends_school_events</t>
+          <t>socioeconomic_vulnerability_score</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.008490303355292699</v>
+        <v>0.01739113126002</v>
+      </c>
+      <c r="C25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>school_enjoyment</t>
+          <t>math_exam_score</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0056394439288733</v>
+        <v>0.0162169629101898</v>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>govt_support</t>
+          <t>school_enjoyment</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0003445954506522</v>
+        <v>0.0099244264960597</v>
+      </c>
+      <c r="C27" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>parent_attends_school_events</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.0093145850924967</v>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>english_exam_score</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.0082984912403191</v>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>geographic_zone</t>
+          <t>parent_guardian_occupation</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.00825879350919</v>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>class_level</t>
+          <t>barriers_to_regular_attendance</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.0065473833031112</v>
+      </c>
+      <c r="C31" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mode_of_transport_to_school</t>
+          <t>own_textbooks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>0.005063814676465</v>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>travel_time_to_school</t>
+          <t>class_level</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>0.001561989449922</v>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -1397,37 +2258,61 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>0.0004929735535397</v>
+      </c>
+      <c r="C34" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>home_has_electricity</t>
+          <t>mode_of_transport_to_school</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>0.0001308053501094</v>
+      </c>
+      <c r="C35" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>safety_at_school</t>
+          <t>govt_support</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>0.0001160384795363</v>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>daily_study_hours_at_home</t>
+          <t>geographic_zone</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>4.343976707678186e-05</v>
+      </c>
+      <c r="C37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="38">
@@ -1437,7 +2322,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>4.195170364032199e-05</v>
+      </c>
+      <c r="C38" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="39">
@@ -1447,7 +2338,219 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>1.938760505432745e-05</v>
+      </c>
+      <c r="C39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.691078786106977e-05</v>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3.454247702568804e-06</v>
+      </c>
+      <c r="C41" t="b">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>home_has_electricity</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>TPR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FPR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TNR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Baseline LightGBM</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E-LightGBM (Proposed)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Subgroup_Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Equal_Opportunity_Diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Equalized_Odds_Diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Within_Threshold</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_Groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.08333333333333337</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.08333333333333337</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>geographic_zone</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
